--- a/data/employees/EMP038/AST-EMP038-06.xlsx
+++ b/data/employees/EMP038/AST-EMP038-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Jamie Brown (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Specialist | Location: Fremont | Date: 2025-02-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>67</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>66</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP038</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp038 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>66</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP038</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp038 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>70</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP038</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp038 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP038</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp038 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>77</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>84</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>87</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>76</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>91</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>94</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>83</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>84</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>72</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>88</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>65</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>74</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp038 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>96</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP038</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP038 contributes to ast emp038 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>